--- a/docs/Reports/deliverables/2026-Q3/PeerLink-KACST-Quarterly-VA-Findings-Register-2026-Q3.xlsx
+++ b/docs/Reports/deliverables/2026-Q3/PeerLink-KACST-Quarterly-VA-Findings-Register-2026-Q3.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t>GitHub reports 24 open npm Dependabot alerts on the default-branch lockfile: 1 Critical, 12 High, 10 Medium, 1 Low. This differs from the assessed production branch.</t>
+          <t>GitHub reports 27 open npm Dependabot alerts on the default-branch lockfile: 1 Critical, 14 High, 11 Medium, 1 Low. This differs from the assessed production branch.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
